--- a/politica_horario.xlsx
+++ b/politica_horario.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lemue\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lemue\Documents\Codex\ElDuendecitoDeVianni\dist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0111858-7389-47A8-AC53-0683A9BACEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F38FC65-A134-4FD9-BA16-04C35FCDC146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1972" yWindow="2213" windowWidth="18001" windowHeight="11977" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="203" yWindow="0" windowWidth="19800" windowHeight="12953" xr2:uid="{EAC128A2-CDB9-48AA-A659-76A596C36B64}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,45 +25,69 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
+  <si>
+    <t>02:30 PM A 10:30 PM *</t>
+  </si>
+  <si>
+    <t>07:00 AM A 03:00 PM*</t>
+  </si>
+  <si>
+    <t>07:00 AM A 07:00 PM (Encargados)</t>
+  </si>
+  <si>
+    <t>08:00 AM A 06:00 PM (Administrativo)*</t>
+  </si>
   <si>
     <t>01:00 PM A 09:00 PM</t>
   </si>
   <si>
+    <t>01:00 PM A 09:00 PM Restaurante *</t>
+  </si>
+  <si>
+    <t>08:00 AM A 06:00 PM (Almacén)*</t>
+  </si>
+  <si>
+    <t>08:00 AM A 06:00 PM (Recepción/Costos) *</t>
+  </si>
+  <si>
+    <t>7:00 PM A 7:00 PM</t>
+  </si>
+  <si>
+    <t>7:00 PM A 7:00 PM (Mercado)</t>
+  </si>
+  <si>
+    <t>02:00 PM A 10:30 PM</t>
+  </si>
+  <si>
+    <t>07:00 AM A 03:00 PM</t>
+  </si>
+  <si>
+    <t>08:00 AM A 05:00 PM (reposteria)*</t>
+  </si>
+  <si>
     <t>02:30 PM A 10:30 PM</t>
   </si>
   <si>
-    <t>07:00 AM A 03:00 PM</t>
-  </si>
-  <si>
-    <t>07:00 AM A 05:00 PM eliminar</t>
-  </si>
-  <si>
-    <t>07:00 AM A 07:00 PM (Encargados)</t>
+    <t>07:00 AM A 07:00 PM</t>
   </si>
   <si>
     <t>08:00 AM A 04:00 PM</t>
   </si>
   <si>
-    <t>08:00 AM A 05:00 PM</t>
-  </si>
-  <si>
-    <t>08:00 AM A 06:00 PM (Almacén)</t>
-  </si>
-  <si>
-    <t>08:00 AM A 06:00 PM (Recepción)</t>
-  </si>
-  <si>
-    <t>08:00 PM A 06:00 PM (Administrativo)</t>
-  </si>
-  <si>
-    <t>08:00 PM A 07:00 PM (Gerente)</t>
-  </si>
-  <si>
-    <t>10:00 AM A 07:00 PM</t>
-  </si>
-  <si>
-    <t>7:00 PM A 7:00 PM (Mercado)</t>
+    <t>10:00 AM A 06:00 PM (panaderia)*</t>
+  </si>
+  <si>
+    <t>10:00 AM A 10:00 PM*</t>
+  </si>
+  <si>
+    <t>08:00 AM A 04:00 PM (ferreteria)*</t>
+  </si>
+  <si>
+    <t>8:00AM a 6:00PM (sup. restaurante)*</t>
+  </si>
+  <si>
+    <t>horario1</t>
   </si>
   <si>
     <t>horario2</t>
@@ -72,50 +96,65 @@
     <t>dias</t>
   </si>
   <si>
+    <t>break</t>
+  </si>
+  <si>
+    <t>feriados</t>
+  </si>
+  <si>
+    <t>12:00 PM A 07:00 PM</t>
+  </si>
+  <si>
+    <t>08:00 AM A 3:00 PM</t>
+  </si>
+  <si>
+    <t>08:00 AM A 4:00 PM (Cocina)*</t>
+  </si>
+  <si>
+    <t>02:00 PM A 08:00 PM</t>
+  </si>
+  <si>
+    <t>08:00 AM A 2:00 PM</t>
+  </si>
+  <si>
+    <t>6:30 AM a 2:30 PM  (seguridad/ limpieza/carniceria)*</t>
+  </si>
+  <si>
+    <t>08:00 AM A 5:00 PM</t>
+  </si>
+  <si>
+    <t>08:00 AM A 12:00 PM</t>
+  </si>
+  <si>
+    <t>08:00 AM A 01:00 PM</t>
+  </si>
+  <si>
     <t>08:00 AM A 02:00 PM</t>
   </si>
   <si>
-    <t>09:00 AM A 03:00 PM</t>
-  </si>
-  <si>
-    <t>09:00 AM A 04:00 PM</t>
-  </si>
-  <si>
-    <t>08:00 AM A 12:00 PM</t>
-  </si>
-  <si>
-    <t>09:00 AM A 12:00 PM</t>
-  </si>
-  <si>
-    <t>09:00 PM A 12:00 PM</t>
-  </si>
-  <si>
-    <t>01:30 PM A 8:30 PM</t>
-  </si>
-  <si>
-    <t>11:00 AM A 06:00 PM</t>
-  </si>
-  <si>
-    <t>8:00 PM A 6:00 PM</t>
-  </si>
-  <si>
-    <t>02:00 PM A 08:00 PM</t>
-  </si>
-  <si>
-    <t>break</t>
-  </si>
-  <si>
-    <t>feriados</t>
-  </si>
-  <si>
-    <t>horario1 (de GridViewExport.xls)</t>
+    <t>10:00 AM A 08:00 PM</t>
+  </si>
+  <si>
+    <t>7:00 AM A 7:00 PM</t>
+  </si>
+  <si>
+    <t>09:00 AM A 5:00 PM</t>
+  </si>
+  <si>
+    <t>9:00 AM a 10:00 PM (seguridad)*</t>
+  </si>
+  <si>
+    <t>09:00 AM A 8:00 PM</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -124,10 +163,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF555555"/>
-      <name val="Arial"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -139,32 +185,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="2"/>
+        <bgColor theme="2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -173,10 +204,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -195,7 +224,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -211,7 +240,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -223,7 +252,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -270,6 +299,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -305,6 +351,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -456,194 +519,221 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF533314-B2C0-43D8-A83B-7ED78E5E503B}">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="43.3984375" customWidth="1"/>
-    <col min="2" max="2" width="21.3984375" customWidth="1"/>
+    <col min="1" max="1" width="46.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.86328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>20</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>20</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>20</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>20</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
         <v>27</v>
       </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="B10" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>20</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="C2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" s="1" t="s">
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12">
+        <v>20</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10">
-        <v>5</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11">
-        <v>6</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12">
-        <v>6</v>
-      </c>
-      <c r="D12">
-        <v>20</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>15</v>
+      <c r="B13" t="s">
+        <v>29</v>
       </c>
       <c r="C13">
         <v>6</v>
@@ -656,11 +746,11 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>18</v>
+      <c r="B14" t="s">
+        <v>32</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -670,11 +760,170 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17">
+        <v>6</v>
+      </c>
+      <c r="D17">
+        <v>20</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>20</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19">
+        <v>6</v>
+      </c>
+      <c r="D19">
+        <v>20</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20">
+        <v>5</v>
+      </c>
+      <c r="D20">
+        <v>20</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21">
+        <v>6</v>
+      </c>
+      <c r="D21">
+        <v>20</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22">
+        <v>6</v>
+      </c>
+      <c r="D22">
+        <v>20</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="G23" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="G24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="G25" t="s">
+        <v>40</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A444">
+    <sortCondition ref="A1:A444"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>